--- a/mes-plugins/mes-plugins-basic/src/main/resources/basic/public/resources/productImportSchema_cn.xlsx
+++ b/mes-plugins/mes-plugins-basic/src/main/resources/basic/public/resources/productImportSchema_cn.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdutka\Desktop\Import templates - 副本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/krna/Projects/mes/mes-plugins/mes-plugins-basic/src/main/resources/basic/public/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2F4BE8E-5A67-4DB4-81F3-AE066EB19316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC920048-93FE-664A-AE17-224AE3C29306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Products" sheetId="1" r:id="rId1"/>
@@ -54,6 +54,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>qcadoo MES:</t>
         </r>
@@ -62,6 +63,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -86,6 +88,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>qcadoo MES:</t>
         </r>
@@ -94,6 +97,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -113,6 +117,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>.</t>
         </r>
@@ -126,6 +131,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>qcadoo MES:</t>
         </r>
@@ -134,6 +140,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -153,6 +160,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">. </t>
         </r>
@@ -171,6 +179,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">:
 - </t>
@@ -190,6 +199,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">,
 - </t>
@@ -209,6 +219,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">,
 - </t>
@@ -228,6 +239,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">, 
 - </t>
@@ -247,6 +259,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">,
 - </t>
@@ -266,6 +279,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>.</t>
         </r>
@@ -279,6 +293,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>qcadoo MES:</t>
         </r>
@@ -287,6 +302,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -306,6 +322,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">. </t>
         </r>
@@ -329,6 +346,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>qcadoo MES:</t>
         </r>
@@ -337,6 +355,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -356,6 +375,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>.</t>
         </r>
@@ -374,6 +394,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve"> </t>
         </r>
@@ -397,6 +418,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>qcadoo MES:</t>
         </r>
@@ -405,6 +427,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -424,6 +447,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">. </t>
         </r>
@@ -442,6 +466,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -461,6 +486,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>:</t>
         </r>
@@ -479,6 +505,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>“box”</t>
         </r>
@@ -497,6 +524,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>“pcs”</t>
         </r>
@@ -515,6 +543,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>10</t>
         </r>
@@ -533,6 +562,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>= 10</t>
         </r>
@@ -556,6 +586,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>qcadoo MES:</t>
         </r>
@@ -564,6 +595,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -583,6 +615,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">. </t>
         </r>
@@ -601,6 +634,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>EAN</t>
         </r>
@@ -619,6 +653,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>:</t>
         </r>
@@ -637,6 +672,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>EAN</t>
         </r>
@@ -660,6 +696,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>qcadoo MES:</t>
         </r>
@@ -668,6 +705,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -687,6 +725,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">. </t>
         </r>
@@ -710,6 +749,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>qcadoo MES:</t>
         </r>
@@ -718,6 +758,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -737,6 +778,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>.</t>
         </r>
@@ -750,6 +792,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>qcadoo MES:</t>
         </r>
@@ -758,6 +801,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -777,6 +821,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>.</t>
         </r>
@@ -800,6 +845,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>qcadoo MES:</t>
         </r>
@@ -808,6 +854,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -827,6 +874,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">. </t>
         </r>
@@ -845,6 +893,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>.</t>
         </r>
@@ -858,6 +907,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>qcadoo MES:</t>
         </r>
@@ -866,6 +916,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -885,6 +936,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">. </t>
         </r>
@@ -903,6 +955,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>qcadoo</t>
         </r>
@@ -926,6 +979,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>qcadoo MES:</t>
         </r>
@@ -934,6 +988,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -953,6 +1008,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>5</t>
         </r>
@@ -971,6 +1027,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>0.12345</t>
         </r>
@@ -984,6 +1041,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>qcadoo MES:</t>
         </r>
@@ -992,6 +1050,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -1011,6 +1070,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>5</t>
         </r>
@@ -1029,6 +1089,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>0.12345</t>
         </r>
@@ -1042,6 +1103,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>qcadoo MES:</t>
         </r>
@@ -1050,6 +1112,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -1069,6 +1132,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>5</t>
         </r>
@@ -1087,6 +1151,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>0.12345</t>
         </r>
@@ -1100,6 +1165,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>qcadoo MES:</t>
         </r>
@@ -1108,6 +1174,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -1127,6 +1194,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>.</t>
         </r>
@@ -1140,6 +1208,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>qcadoo MES:</t>
         </r>
@@ -1148,6 +1217,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -1172,6 +1242,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>qcadoo MES:</t>
         </r>
@@ -1180,6 +1251,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -1199,6 +1271,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">. </t>
         </r>
@@ -1217,6 +1290,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve"> '</t>
         </r>
@@ -1235,6 +1309,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">' </t>
         </r>
@@ -1253,6 +1328,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve"> '</t>
         </r>
@@ -1271,6 +1347,7 @@
             <sz val="11"/>
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
+            <family val="2"/>
           </rPr>
           <t>'.</t>
         </r>
@@ -1281,7 +1358,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Y/N</t>
   </si>
@@ -1399,6 +1476,9 @@
   <si>
     <t>包装品</t>
   </si>
+  <si>
+    <t>Expiration date evidence</t>
+  </si>
 </sst>
 </file>
 
@@ -1440,11 +1520,13 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1538,9 +1620,28 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normalny" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="22">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1946,7 +2047,7 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Styl tabeli 1" pivot="0" count="1" xr9:uid="{5916ACAE-860C-41DE-93CE-65C632F1090D}">
-      <tableStyleElement type="wholeTable" dxfId="20"/>
+      <tableStyleElement type="wholeTable" dxfId="21"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2603,27 +2704,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3EF1E979-207E-47C4-9AFE-5BA280F7BEEC}" name="productImportSchema_en" displayName="productImportSchema_en" ref="A1:R2" insertRow="1" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
-  <autoFilter ref="A1:R2" xr:uid="{3EF1E979-207E-47C4-9AFE-5BA280F7BEEC}"/>
-  <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{2C201668-3CD6-489F-809C-EFB4F2E697A6}" name="产品编号" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{BED42B7C-AA1C-4D86-A97D-42DFF2ABFC99}" name="产品名称" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{2BD0676B-09A5-4D52-8D38-762C5FC845F5}" name="物料类型" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{C478A5DE-164D-4B5E-B227-B82363809398}" name="默认单位" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{3ECE3C08-28FA-455A-809D-5D8C51C53951}" name="附加单位" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{D6356E1B-1498-4F42-8E53-B5E002D3ADD8}" name="单位换算" dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{F93F6B18-4CC2-4826-8065-0BAC652D8244}" name="EAN 编码" dataDxfId="11"/>
-    <tableColumn id="8" xr3:uid="{F57ED3FB-C444-4D0D-9912-DFCBFC297B8C}" name="种类" dataDxfId="10"/>
-    <tableColumn id="9" xr3:uid="{F16578D4-258B-4578-BE1C-484CCC898684}" name="描述" dataDxfId="9"/>
-    <tableColumn id="10" xr3:uid="{483CFD25-B432-4F34-9C86-0D60BA26D995}" name="制造商" dataDxfId="8"/>
-    <tableColumn id="11" xr3:uid="{CD301045-E17B-4F44-A794-67E6CBA37A43}" name="分类" dataDxfId="7"/>
-    <tableColumn id="12" xr3:uid="{F8FE13EF-6730-42F0-92D7-8A2A9C0F0F90}" name="所属系列" dataDxfId="6"/>
-    <tableColumn id="13" xr3:uid="{EC10C708-462E-42D9-9789-115BB59EC60F}" name="名义成本" dataDxfId="5"/>
-    <tableColumn id="14" xr3:uid="{20E3562B-134E-4CEC-8D4B-FA4A24FAB1C9}" name="最新采购成本" dataDxfId="4"/>
-    <tableColumn id="15" xr3:uid="{B9A08066-9499-46BD-B4BA-457BB4EB7E4A}" name="平均成本" dataDxfId="3"/>
-    <tableColumn id="16" xr3:uid="{BA516DDF-89CD-4830-8234-28B7361601F4}" name="尺寸" dataDxfId="2"/>
-    <tableColumn id="17" xr3:uid="{2E84D04E-647F-4253-8983-F87E0652FDD8}" name="有效期" dataDxfId="1"/>
-    <tableColumn id="18" xr3:uid="{E00DEA52-A691-460C-978D-6D41BD23C0AF}" name="批次依据" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3EF1E979-207E-47C4-9AFE-5BA280F7BEEC}" name="productImportSchema_en" displayName="productImportSchema_en" ref="A1:S2" insertRow="1" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+  <autoFilter ref="A1:S2" xr:uid="{3EF1E979-207E-47C4-9AFE-5BA280F7BEEC}"/>
+  <tableColumns count="19">
+    <tableColumn id="1" xr3:uid="{2C201668-3CD6-489F-809C-EFB4F2E697A6}" name="产品编号" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{BED42B7C-AA1C-4D86-A97D-42DFF2ABFC99}" name="产品名称" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{2BD0676B-09A5-4D52-8D38-762C5FC845F5}" name="物料类型" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{C478A5DE-164D-4B5E-B227-B82363809398}" name="默认单位" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{3ECE3C08-28FA-455A-809D-5D8C51C53951}" name="附加单位" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{D6356E1B-1498-4F42-8E53-B5E002D3ADD8}" name="单位换算" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{F93F6B18-4CC2-4826-8065-0BAC652D8244}" name="EAN 编码" dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{F57ED3FB-C444-4D0D-9912-DFCBFC297B8C}" name="种类" dataDxfId="11"/>
+    <tableColumn id="9" xr3:uid="{F16578D4-258B-4578-BE1C-484CCC898684}" name="描述" dataDxfId="10"/>
+    <tableColumn id="10" xr3:uid="{483CFD25-B432-4F34-9C86-0D60BA26D995}" name="制造商" dataDxfId="9"/>
+    <tableColumn id="11" xr3:uid="{CD301045-E17B-4F44-A794-67E6CBA37A43}" name="分类" dataDxfId="8"/>
+    <tableColumn id="12" xr3:uid="{F8FE13EF-6730-42F0-92D7-8A2A9C0F0F90}" name="所属系列" dataDxfId="7"/>
+    <tableColumn id="13" xr3:uid="{EC10C708-462E-42D9-9789-115BB59EC60F}" name="名义成本" dataDxfId="6"/>
+    <tableColumn id="14" xr3:uid="{20E3562B-134E-4CEC-8D4B-FA4A24FAB1C9}" name="最新采购成本" dataDxfId="5"/>
+    <tableColumn id="15" xr3:uid="{B9A08066-9499-46BD-B4BA-457BB4EB7E4A}" name="平均成本" dataDxfId="4"/>
+    <tableColumn id="16" xr3:uid="{BA516DDF-89CD-4830-8234-28B7361601F4}" name="尺寸" dataDxfId="3"/>
+    <tableColumn id="17" xr3:uid="{2E84D04E-647F-4253-8983-F87E0652FDD8}" name="有效期" dataDxfId="2"/>
+    <tableColumn id="18" xr3:uid="{E00DEA52-A691-460C-978D-6D41BD23C0AF}" name="批次依据" dataDxfId="1"/>
+    <tableColumn id="19" xr3:uid="{48A8DDB9-8367-1845-AFE8-B6352E32B5F5}" name="Expiration date evidence" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="Styl tabeli 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2650,9 +2752,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motyw pakietu Office 2013–2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Pakiet Office 2013–2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2690,7 +2792,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Pakiet Office 2013–2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2796,7 +2898,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Pakiet Office 2013–2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2938,7 +3040,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2949,20 +3051,20 @@
   <sheetPr>
     <tabColor theme="9"/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75"/>
+  <dimension ref="A1:S2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="2" width="16.875" style="1" customWidth="1"/>
+    <col min="1" max="2" width="16.83203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="22.5" style="1" customWidth="1"/>
-    <col min="4" max="5" width="20.875" style="1" customWidth="1"/>
-    <col min="6" max="11" width="16.875" style="1" customWidth="1"/>
+    <col min="4" max="5" width="20.83203125" style="1" customWidth="1"/>
+    <col min="6" max="11" width="16.83203125" style="1" customWidth="1"/>
     <col min="12" max="12" width="17.5" style="1" customWidth="1"/>
-    <col min="13" max="15" width="20.875" style="1" customWidth="1"/>
-    <col min="16" max="18" width="16.875" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="8.875" style="1"/>
+    <col min="13" max="15" width="20.83203125" style="1" customWidth="1"/>
+    <col min="16" max="18" width="16.83203125" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:19">
       <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
@@ -3017,8 +3119,11 @@
       <c r="R1" s="8" t="s">
         <v>18</v>
       </c>
+      <c r="S1" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:19">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="D2" s="2"/>
@@ -3063,7 +3168,7 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="22.5" customWidth="1"/>
   </cols>
